--- a/Sistemi_sablon.xlsx
+++ b/Sistemi_sablon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andra\PycharmProjects\Horses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C68936-DA26-4B65-9A65-9325886F1CCF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D06D8E-BB63-4912-ABD8-27A0330ED711}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18600" yWindow="0" windowWidth="20880" windowHeight="8430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2485,7 +2485,7 @@
         <v>117</v>
       </c>
       <c r="O22" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.25">
@@ -3342,7 +3342,7 @@
         <v>2</v>
       </c>
       <c r="O71" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="T71" t="s">
         <v>225</v>
@@ -3422,7 +3422,7 @@
         <v>231</v>
       </c>
       <c r="O75" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="S75" t="s">
         <v>90</v>
@@ -3556,7 +3556,7 @@
         <v>82</v>
       </c>
       <c r="O82" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="R82" t="s">
         <v>86</v>
@@ -3711,7 +3711,7 @@
         <v>263</v>
       </c>
       <c r="O89" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="S89">
         <v>1</v>
@@ -3751,7 +3751,7 @@
         <v>238</v>
       </c>
       <c r="O91" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="AC91" t="s">
         <v>180</v>
@@ -3791,7 +3791,7 @@
         <v>274</v>
       </c>
       <c r="O93" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="T93" t="s">
         <v>146</v>
@@ -4119,7 +4119,7 @@
         <v>190</v>
       </c>
       <c r="O113" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="Y113" t="s">
         <v>410</v>
